--- a/docs/08_Remediation/v0_v1_comparison.xlsx
+++ b/docs/08_Remediation/v0_v1_comparison.xlsx
@@ -765,12 +765,12 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>46.1% (355/770 lines)</t>
+          <t>45.84% (353/770 lines)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>46.1% (355/770 lines)</t>
+          <t>45.84% (353/770 lines)</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
